--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/holyship/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="13_ncr:1_{FB02597B-DDFD-481B-B7DE-A53AD49E1F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F975CF5-BB8E-4F2F-BFC9-EC3812C24276}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="13_ncr:1_{FB02597B-DDFD-481B-B7DE-A53AD49E1F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C3E3C8E-D7DD-474F-958E-A277034C01AD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="72">
   <si>
     <t>Name</t>
   </si>
@@ -242,6 +242,15 @@
   </si>
   <si>
     <t>Mythic III</t>
+  </si>
+  <si>
+    <t>Luminus</t>
+  </si>
+  <si>
+    <t>CloverZ</t>
+  </si>
+  <si>
+    <t>Left</t>
   </si>
 </sst>
 </file>
@@ -361,10 +370,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -652,7 +657,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1144,7 +1149,7 @@
         <v>Iron I</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>5</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -1162,7 +1167,7 @@
         <v>Iron I</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>5</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -1216,6 +1221,42 @@
         <v>#N/A</v>
       </c>
       <c r="E31" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B32" s="4">
+        <v>2886</v>
+      </c>
+      <c r="C32" s="4">
+        <v>1000</v>
+      </c>
+      <c r="D32" s="4" t="str">
+        <f>_xlfn.XLOOKUP(C32,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
+        <v>Iron I</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B33" s="4">
+        <v>3480</v>
+      </c>
+      <c r="C33" s="4">
+        <v>0</v>
+      </c>
+      <c r="D33" s="4" t="e">
+        <f>_xlfn.XLOOKUP(C33,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E33" s="5" t="s">
         <v>5</v>
       </c>
     </row>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="67" documentId="13_ncr:1_{FB02597B-DDFD-481B-B7DE-A53AD49E1F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C3E3C8E-D7DD-474F-958E-A277034C01AD}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="13_ncr:1_{FB02597B-DDFD-481B-B7DE-A53AD49E1F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B95E6DF1-D060-4403-BA54-F68CE4520CCD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -370,6 +370,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1247,7 +1251,7 @@
         <v>70</v>
       </c>
       <c r="B33" s="4">
-        <v>3480</v>
+        <v>3481</v>
       </c>
       <c r="C33" s="4">
         <v>0</v>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="13_ncr:1_{FB02597B-DDFD-481B-B7DE-A53AD49E1F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B95E6DF1-D060-4403-BA54-F68CE4520CCD}"/>
+  <xr:revisionPtr revIDLastSave="108" documentId="13_ncr:1_{FB02597B-DDFD-481B-B7DE-A53AD49E1F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{068E38A3-8F21-4EA3-851F-E33805CA37D7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -696,11 +696,11 @@
         <v>9692</v>
       </c>
       <c r="C2" s="4">
-        <v>3307</v>
-      </c>
-      <c r="D2" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4" t="e">
         <f>_xlfn.XLOOKUP(C2,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Mythic I</v>
+        <v>#N/A</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>5</v>
@@ -708,17 +708,17 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B3" s="5">
-        <v>7042</v>
+        <v>5873</v>
       </c>
       <c r="C3" s="4">
-        <v>3178</v>
-      </c>
-      <c r="D3" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4" t="e">
         <f>_xlfn.XLOOKUP(C3,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Mythic I</v>
+        <v>#N/A</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>5</v>
@@ -726,17 +726,17 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="5">
-        <v>5464</v>
+        <v>25</v>
+      </c>
+      <c r="B4" s="4">
+        <v>8153</v>
       </c>
       <c r="C4" s="4">
-        <v>3156</v>
+        <v>2155</v>
       </c>
       <c r="D4" s="4" t="str">
         <f>_xlfn.XLOOKUP(C4,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Mythic I</v>
+        <v>Gold III</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>5</v>
@@ -744,17 +744,17 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="5">
-        <v>9706</v>
+        <v>35</v>
+      </c>
+      <c r="B5" s="4">
+        <v>6654</v>
       </c>
       <c r="C5" s="4">
-        <v>3123</v>
+        <v>1000</v>
       </c>
       <c r="D5" s="4" t="str">
         <f>_xlfn.XLOOKUP(C5,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Mythic I</v>
+        <v>Iron I</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>5</v>
@@ -762,17 +762,17 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="5">
-        <v>6455</v>
+        <v>34</v>
+      </c>
+      <c r="B6" s="4">
+        <v>5161</v>
       </c>
       <c r="C6" s="4">
-        <v>3122</v>
+        <v>1300</v>
       </c>
       <c r="D6" s="4" t="str">
         <f>_xlfn.XLOOKUP(C6,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Mythic I</v>
+        <v>Bronze I</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>5</v>
@@ -780,17 +780,17 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="5">
-        <v>8128</v>
-      </c>
-      <c r="C7" s="4">
-        <v>3107</v>
-      </c>
-      <c r="D7" s="4" t="str">
+        <v>42</v>
+      </c>
+      <c r="B7" s="4">
+        <v>3194</v>
+      </c>
+      <c r="C7" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D7" s="4" t="e">
         <f>_xlfn.XLOOKUP(C7,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Mythic I</v>
+        <v>#N/A</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>5</v>
@@ -798,17 +798,17 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="5">
-        <v>5873</v>
+        <v>32</v>
+      </c>
+      <c r="B8" s="4">
+        <v>8334</v>
       </c>
       <c r="C8" s="4">
-        <v>3100</v>
+        <v>1640</v>
       </c>
       <c r="D8" s="4" t="str">
         <f>_xlfn.XLOOKUP(C8,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Mythic I</v>
+        <v>Silver I</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>5</v>
@@ -816,17 +816,17 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="5">
-        <v>7411</v>
+        <v>37</v>
+      </c>
+      <c r="B9" s="4">
+        <v>804</v>
       </c>
       <c r="C9" s="4">
-        <v>3091</v>
+        <v>1000</v>
       </c>
       <c r="D9" s="4" t="str">
         <f>_xlfn.XLOOKUP(C9,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Master III</v>
+        <v>Iron I</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>5</v>
@@ -834,17 +834,17 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B10" s="5">
-        <v>1025</v>
+        <v>7042</v>
       </c>
       <c r="C10" s="4">
-        <v>3005</v>
+        <v>2515</v>
       </c>
       <c r="D10" s="4" t="str">
         <f>_xlfn.XLOOKUP(C10,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Master III</v>
+        <v>Diamond I</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>5</v>
@@ -852,17 +852,17 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B11" s="5">
-        <v>5078</v>
+        <v>9706</v>
       </c>
       <c r="C11" s="4">
-        <v>2928</v>
+        <v>2238</v>
       </c>
       <c r="D11" s="4" t="str">
         <f>_xlfn.XLOOKUP(C11,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Master II</v>
+        <v>Platinum I</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>5</v>
@@ -870,17 +870,17 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B12" s="5">
-        <v>5101</v>
+        <v>5464</v>
       </c>
       <c r="C12" s="4">
-        <v>2914</v>
-      </c>
-      <c r="D12" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="D12" s="4" t="e">
         <f>_xlfn.XLOOKUP(C12,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Master II</v>
+        <v>#N/A</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>5</v>
@@ -888,17 +888,17 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="5">
-        <v>5566</v>
+        <v>29</v>
+      </c>
+      <c r="B13" s="4">
+        <v>7449</v>
       </c>
       <c r="C13" s="4">
-        <v>2874</v>
+        <v>1740</v>
       </c>
       <c r="D13" s="4" t="str">
         <f>_xlfn.XLOOKUP(C13,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Master I</v>
+        <v>Silver II</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>5</v>
@@ -906,17 +906,17 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B14" s="4">
-        <v>8153</v>
+        <v>3480</v>
       </c>
       <c r="C14" s="4">
-        <v>2817</v>
+        <v>1736</v>
       </c>
       <c r="D14" s="4" t="str">
         <f>_xlfn.XLOOKUP(C14,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Master I</v>
+        <v>Silver II</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>5</v>
@@ -924,17 +924,17 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="B15" s="4">
-        <v>168</v>
-      </c>
-      <c r="C15" s="4">
-        <v>2800</v>
-      </c>
-      <c r="D15" s="4" t="str">
+        <v>3481</v>
+      </c>
+      <c r="C15" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D15" s="4" t="e">
         <f>_xlfn.XLOOKUP(C15,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Master I</v>
+        <v>#N/A</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>5</v>
@@ -942,17 +942,17 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="4">
-        <v>452</v>
+        <v>22</v>
+      </c>
+      <c r="B16" s="5">
+        <v>5078</v>
       </c>
       <c r="C16" s="4">
-        <v>2790</v>
+        <v>2364</v>
       </c>
       <c r="D16" s="4" t="str">
         <f>_xlfn.XLOOKUP(C16,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Diamond III</v>
+        <v>Platinum II</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>5</v>
@@ -960,35 +960,35 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="B17" s="4">
-        <v>9881</v>
-      </c>
-      <c r="C17" s="4">
-        <v>2747</v>
-      </c>
-      <c r="D17" s="4" t="str">
+        <v>7120</v>
+      </c>
+      <c r="C17" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D17" s="4" t="e">
         <f>_xlfn.XLOOKUP(C17,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Diamond III</v>
+        <v>#N/A</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>5</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B18" s="4">
-        <v>7449</v>
+        <v>17</v>
+      </c>
+      <c r="B18" s="5">
+        <v>6455</v>
       </c>
       <c r="C18" s="4">
-        <v>2643</v>
+        <v>2393</v>
       </c>
       <c r="D18" s="4" t="str">
         <f>_xlfn.XLOOKUP(C18,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Diamond II</v>
+        <v>Platinum II</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>5</v>
@@ -996,17 +996,17 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="B19" s="4">
-        <v>5297</v>
+        <v>2886</v>
       </c>
       <c r="C19" s="4">
-        <v>2578</v>
+        <v>1808</v>
       </c>
       <c r="D19" s="4" t="str">
         <f>_xlfn.XLOOKUP(C19,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Diamond I</v>
+        <v>Silver III</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>5</v>
@@ -1014,17 +1014,17 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" s="4">
-        <v>3528</v>
+        <v>21</v>
+      </c>
+      <c r="B20" s="5">
+        <v>1025</v>
       </c>
       <c r="C20" s="4">
-        <v>2527</v>
+        <v>2074</v>
       </c>
       <c r="D20" s="4" t="str">
         <f>_xlfn.XLOOKUP(C20,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Diamond I</v>
+        <v>Gold II</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>5</v>
@@ -1032,17 +1032,17 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B21" s="4">
-        <v>8334</v>
+        <v>3528</v>
       </c>
       <c r="C21" s="4">
-        <v>2526</v>
+        <v>1600</v>
       </c>
       <c r="D21" s="4" t="str">
         <f>_xlfn.XLOOKUP(C21,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Diamond I</v>
+        <v>Silver I</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>5</v>
@@ -1050,17 +1050,17 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B22" s="4">
-        <v>3480</v>
+        <v>168</v>
       </c>
       <c r="C22" s="4">
-        <v>2394</v>
+        <v>2173</v>
       </c>
       <c r="D22" s="4" t="str">
         <f>_xlfn.XLOOKUP(C22,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Platinum II</v>
+        <v>Gold III</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>5</v>
@@ -1068,17 +1068,17 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B23" s="4">
-        <v>5161</v>
+        <v>23</v>
+      </c>
+      <c r="B23" s="5">
+        <v>5101</v>
       </c>
       <c r="C23" s="4">
-        <v>2241</v>
+        <v>2302</v>
       </c>
       <c r="D23" s="4" t="str">
         <f>_xlfn.XLOOKUP(C23,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Platinum I</v>
+        <v>Platinum II</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>5</v>
@@ -1086,17 +1086,17 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B24" s="4">
-        <v>6654</v>
-      </c>
-      <c r="C24" s="4">
-        <v>1956</v>
-      </c>
-      <c r="D24" s="4" t="str">
+        <v>2359</v>
+      </c>
+      <c r="C24" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D24" s="4" t="e">
         <f>_xlfn.XLOOKUP(C24,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Gold I</v>
+        <v>#N/A</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>5</v>
@@ -1110,11 +1110,11 @@
         <v>6698</v>
       </c>
       <c r="C25" s="4">
-        <v>1924</v>
+        <v>1000</v>
       </c>
       <c r="D25" s="4" t="str">
         <f>_xlfn.XLOOKUP(C25,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Gold I</v>
+        <v>Iron I</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>5</v>
@@ -1122,71 +1122,71 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B26" s="4">
-        <v>804</v>
-      </c>
-      <c r="C26" s="4">
-        <v>1182</v>
-      </c>
-      <c r="D26" s="4" t="str">
+        <v>3929</v>
+      </c>
+      <c r="C26" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D26" s="4" t="e">
         <f>_xlfn.XLOOKUP(C26,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Iron II</v>
+        <v>#N/A</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>5</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="4">
-        <v>7120</v>
+        <v>18</v>
+      </c>
+      <c r="B27" s="5">
+        <v>8128</v>
       </c>
       <c r="C27" s="4">
-        <v>1000</v>
+        <v>2513</v>
       </c>
       <c r="D27" s="4" t="str">
         <f>_xlfn.XLOOKUP(C27,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Iron I</v>
+        <v>Diamond I</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>71</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B28" s="4">
-        <v>3929</v>
-      </c>
-      <c r="C28" s="4">
-        <v>1000</v>
-      </c>
-      <c r="D28" s="4" t="str">
+        <v>1004</v>
+      </c>
+      <c r="C28" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D28" s="4" t="e">
         <f>_xlfn.XLOOKUP(C28,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Iron I</v>
+        <v>#N/A</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>71</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="B29" s="4">
-        <v>3194</v>
+        <v>452</v>
       </c>
       <c r="C29" s="4">
-        <v>0</v>
-      </c>
-      <c r="D29" s="4" t="e">
+        <v>2111</v>
+      </c>
+      <c r="D29" s="4" t="str">
         <f>_xlfn.XLOOKUP(C29,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>#N/A</v>
+        <v>Gold III</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>5</v>
@@ -1194,17 +1194,17 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B30" s="4">
-        <v>2359</v>
+        <v>5297</v>
       </c>
       <c r="C30" s="4">
-        <v>0</v>
-      </c>
-      <c r="D30" s="4" t="e">
+        <v>1840</v>
+      </c>
+      <c r="D30" s="4" t="str">
         <f>_xlfn.XLOOKUP(C30,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>#N/A</v>
+        <v>Silver III</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>5</v>
@@ -1212,17 +1212,17 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="B31" s="4">
-        <v>1004</v>
+        <v>9881</v>
       </c>
       <c r="C31" s="4">
-        <v>0</v>
-      </c>
-      <c r="D31" s="4" t="e">
+        <v>2066</v>
+      </c>
+      <c r="D31" s="4" t="str">
         <f>_xlfn.XLOOKUP(C31,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>#N/A</v>
+        <v>Gold II</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>5</v>
@@ -1230,17 +1230,17 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B32" s="4">
-        <v>2886</v>
+        <v>20</v>
+      </c>
+      <c r="B32" s="5">
+        <v>7411</v>
       </c>
       <c r="C32" s="4">
-        <v>1000</v>
+        <v>2365</v>
       </c>
       <c r="D32" s="4" t="str">
         <f>_xlfn.XLOOKUP(C32,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Iron I</v>
+        <v>Platinum II</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>5</v>
@@ -1248,10 +1248,10 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B33" s="4">
-        <v>3481</v>
+        <v>24</v>
+      </c>
+      <c r="B33" s="5">
+        <v>5566</v>
       </c>
       <c r="C33" s="4">
         <v>0</v>
@@ -1265,8 +1265,8 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E31">
-    <sortCondition descending="1" ref="C2:C31"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:E33">
+    <sortCondition ref="A5:A33"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="108" documentId="13_ncr:1_{FB02597B-DDFD-481B-B7DE-A53AD49E1F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{068E38A3-8F21-4EA3-851F-E33805CA37D7}"/>
+  <xr:revisionPtr revIDLastSave="134" documentId="13_ncr:1_{FB02597B-DDFD-481B-B7DE-A53AD49E1F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43E09450-8B77-45B4-B1F8-E8972127F04D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="74">
   <si>
     <t>Name</t>
   </si>
@@ -251,6 +251,12 @@
   </si>
   <si>
     <t>Left</t>
+  </si>
+  <si>
+    <t>หอมหอย</t>
+  </si>
+  <si>
+    <t>GMMFAFA</t>
   </si>
 </sst>
 </file>
@@ -359,7 +365,18 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{6E89C84C-1F9E-4459-82E7-79CF84926B43}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -661,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -726,17 +743,17 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="4">
-        <v>8153</v>
-      </c>
-      <c r="C4" s="4">
-        <v>2155</v>
-      </c>
-      <c r="D4" s="4" t="str">
+        <v>72</v>
+      </c>
+      <c r="B4" s="5">
+        <v>7351</v>
+      </c>
+      <c r="C4" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D4" s="4" t="e">
         <f>_xlfn.XLOOKUP(C4,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Gold III</v>
+        <v>#N/A</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>5</v>
@@ -744,17 +761,17 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B5" s="4">
-        <v>6654</v>
+        <v>8153</v>
       </c>
       <c r="C5" s="4">
-        <v>1000</v>
+        <v>2155</v>
       </c>
       <c r="D5" s="4" t="str">
         <f>_xlfn.XLOOKUP(C5,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Iron I</v>
+        <v>Gold III</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>5</v>
@@ -762,17 +779,17 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" s="4">
-        <v>5161</v>
+        <v>6654</v>
       </c>
       <c r="C6" s="4">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="D6" s="4" t="str">
         <f>_xlfn.XLOOKUP(C6,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Bronze I</v>
+        <v>Iron I</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>5</v>
@@ -780,17 +797,17 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B7" s="4">
-        <v>3194</v>
-      </c>
-      <c r="C7" s="4" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D7" s="4" t="e">
+        <v>5161</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1300</v>
+      </c>
+      <c r="D7" s="4" t="str">
         <f>_xlfn.XLOOKUP(C7,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>#N/A</v>
+        <v>Bronze I</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>5</v>
@@ -798,17 +815,17 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B8" s="4">
-        <v>8334</v>
-      </c>
-      <c r="C8" s="4">
-        <v>1640</v>
-      </c>
-      <c r="D8" s="4" t="str">
+        <v>3194</v>
+      </c>
+      <c r="C8" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D8" s="4" t="e">
         <f>_xlfn.XLOOKUP(C8,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Silver I</v>
+        <v>#N/A</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>5</v>
@@ -960,20 +977,20 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="4">
-        <v>7120</v>
-      </c>
-      <c r="C17" s="4" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D17" s="4" t="e">
+        <v>73</v>
+      </c>
+      <c r="B17" s="5">
+        <v>4713</v>
+      </c>
+      <c r="C17" s="4">
+        <v>1080</v>
+      </c>
+      <c r="D17" s="4" t="str">
         <f>_xlfn.XLOOKUP(C17,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>#N/A</v>
+        <v>Iron I</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>71</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -1122,35 +1139,35 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" s="4">
-        <v>3929</v>
-      </c>
-      <c r="C26" s="4" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D26" s="4" t="e">
+        <v>18</v>
+      </c>
+      <c r="B26" s="5">
+        <v>8128</v>
+      </c>
+      <c r="C26" s="4">
+        <v>2513</v>
+      </c>
+      <c r="D26" s="4" t="str">
         <f>_xlfn.XLOOKUP(C26,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>#N/A</v>
+        <v>Diamond I</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>71</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B27" s="5">
-        <v>8128</v>
-      </c>
-      <c r="C27" s="4">
-        <v>2513</v>
-      </c>
-      <c r="D27" s="4" t="str">
+        <v>41</v>
+      </c>
+      <c r="B27" s="4">
+        <v>1004</v>
+      </c>
+      <c r="C27" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D27" s="4" t="e">
         <f>_xlfn.XLOOKUP(C27,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Diamond I</v>
+        <v>#N/A</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>5</v>
@@ -1158,17 +1175,17 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B28" s="4">
-        <v>1004</v>
-      </c>
-      <c r="C28" s="4" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D28" s="4" t="e">
+        <v>452</v>
+      </c>
+      <c r="C28" s="4">
+        <v>2111</v>
+      </c>
+      <c r="D28" s="4" t="str">
         <f>_xlfn.XLOOKUP(C28,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>#N/A</v>
+        <v>Gold III</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>5</v>
@@ -1176,17 +1193,17 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" s="4">
-        <v>452</v>
+        <v>9881</v>
       </c>
       <c r="C29" s="4">
-        <v>2111</v>
+        <v>2066</v>
       </c>
       <c r="D29" s="4" t="str">
         <f>_xlfn.XLOOKUP(C29,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Gold III</v>
+        <v>Gold II</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>5</v>
@@ -1194,17 +1211,17 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="4">
-        <v>5297</v>
+        <v>20</v>
+      </c>
+      <c r="B30" s="5">
+        <v>7411</v>
       </c>
       <c r="C30" s="4">
-        <v>1840</v>
+        <v>2365</v>
       </c>
       <c r="D30" s="4" t="str">
         <f>_xlfn.XLOOKUP(C30,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Silver III</v>
+        <v>Platinum II</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>5</v>
@@ -1212,17 +1229,17 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31" s="4">
-        <v>9881</v>
+        <v>24</v>
+      </c>
+      <c r="B31" s="5">
+        <v>5566</v>
       </c>
       <c r="C31" s="4">
-        <v>2066</v>
-      </c>
-      <c r="D31" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="D31" s="4" t="e">
         <f>_xlfn.XLOOKUP(C31,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Gold II</v>
+        <v>#N/A</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>5</v>
@@ -1230,44 +1247,83 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B32" s="5">
-        <v>7411</v>
+        <v>32</v>
+      </c>
+      <c r="B32" s="4">
+        <v>8334</v>
       </c>
       <c r="C32" s="4">
-        <v>2365</v>
+        <v>1640</v>
       </c>
       <c r="D32" s="4" t="str">
         <f>_xlfn.XLOOKUP(C32,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Platinum II</v>
+        <v>Silver I</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>5</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B33" s="5">
-        <v>5566</v>
-      </c>
-      <c r="C33" s="4">
-        <v>0</v>
+        <v>38</v>
+      </c>
+      <c r="B33" s="4">
+        <v>7120</v>
+      </c>
+      <c r="C33" s="4" t="e">
+        <v>#N/A</v>
       </c>
       <c r="D33" s="4" t="e">
         <f>_xlfn.XLOOKUP(C33,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
         <v>#N/A</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>5</v>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="4">
+        <v>3929</v>
+      </c>
+      <c r="C34" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D34" s="4" t="e">
+        <f>_xlfn.XLOOKUP(C34,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B35" s="4">
+        <v>5297</v>
+      </c>
+      <c r="C35" s="4">
+        <v>1840</v>
+      </c>
+      <c r="D35" s="4" t="str">
+        <f>_xlfn.XLOOKUP(C35,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
+        <v>Silver III</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:E33">
-    <sortCondition ref="A5:A33"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A33:E35">
+    <sortCondition ref="A32:A35"/>
   </sortState>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="134" documentId="13_ncr:1_{FB02597B-DDFD-481B-B7DE-A53AD49E1F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43E09450-8B77-45B4-B1F8-E8972127F04D}"/>
+  <xr:revisionPtr revIDLastSave="158" documentId="13_ncr:1_{FB02597B-DDFD-481B-B7DE-A53AD49E1F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33D84C9F-5898-4EFD-8E64-B5B3CA8B7EC2}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="0" windowWidth="10260" windowHeight="12072" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Players" sheetId="1" r:id="rId1"/>
@@ -713,11 +713,11 @@
         <v>9692</v>
       </c>
       <c r="C2" s="4">
-        <v>0</v>
-      </c>
-      <c r="D2" s="4" t="e">
+        <v>2592</v>
+      </c>
+      <c r="D2" s="4" t="str">
         <f>_xlfn.XLOOKUP(C2,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>#N/A</v>
+        <v>Diamond I</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>5</v>
@@ -731,11 +731,11 @@
         <v>5873</v>
       </c>
       <c r="C3" s="4">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4" t="e">
+        <v>2367</v>
+      </c>
+      <c r="D3" s="4" t="str">
         <f>_xlfn.XLOOKUP(C3,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>#N/A</v>
+        <v>Platinum II</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>5</v>
@@ -767,11 +767,11 @@
         <v>8153</v>
       </c>
       <c r="C5" s="4">
-        <v>2155</v>
+        <v>2478</v>
       </c>
       <c r="D5" s="4" t="str">
         <f>_xlfn.XLOOKUP(C5,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Gold III</v>
+        <v>Platinum III</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>5</v>
@@ -785,11 +785,11 @@
         <v>6654</v>
       </c>
       <c r="C6" s="4">
-        <v>1000</v>
+        <v>1222</v>
       </c>
       <c r="D6" s="4" t="str">
         <f>_xlfn.XLOOKUP(C6,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Iron I</v>
+        <v>Iron III</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>5</v>
@@ -803,11 +803,11 @@
         <v>5161</v>
       </c>
       <c r="C7" s="4">
-        <v>1300</v>
+        <v>1987</v>
       </c>
       <c r="D7" s="4" t="str">
         <f>_xlfn.XLOOKUP(C7,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Bronze I</v>
+        <v>Gold I</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>5</v>
@@ -857,11 +857,11 @@
         <v>7042</v>
       </c>
       <c r="C10" s="4">
-        <v>2515</v>
+        <v>2744</v>
       </c>
       <c r="D10" s="4" t="str">
         <f>_xlfn.XLOOKUP(C10,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Diamond I</v>
+        <v>Diamond III</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>5</v>
@@ -875,11 +875,11 @@
         <v>9706</v>
       </c>
       <c r="C11" s="4">
-        <v>2238</v>
+        <v>2579</v>
       </c>
       <c r="D11" s="4" t="str">
         <f>_xlfn.XLOOKUP(C11,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Platinum I</v>
+        <v>Diamond I</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>5</v>
@@ -893,11 +893,11 @@
         <v>5464</v>
       </c>
       <c r="C12" s="4">
-        <v>0</v>
-      </c>
-      <c r="D12" s="4" t="e">
+        <v>2504</v>
+      </c>
+      <c r="D12" s="4" t="str">
         <f>_xlfn.XLOOKUP(C12,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>#N/A</v>
+        <v>Diamond I</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>5</v>
@@ -911,11 +911,11 @@
         <v>7449</v>
       </c>
       <c r="C13" s="4">
-        <v>1740</v>
+        <v>2245</v>
       </c>
       <c r="D13" s="4" t="str">
         <f>_xlfn.XLOOKUP(C13,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Silver II</v>
+        <v>Platinum I</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>5</v>
@@ -929,11 +929,11 @@
         <v>3480</v>
       </c>
       <c r="C14" s="4">
-        <v>1736</v>
+        <v>2163</v>
       </c>
       <c r="D14" s="4" t="str">
         <f>_xlfn.XLOOKUP(C14,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Silver II</v>
+        <v>Gold III</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>5</v>
@@ -965,11 +965,11 @@
         <v>5078</v>
       </c>
       <c r="C16" s="4">
-        <v>2364</v>
+        <v>2497</v>
       </c>
       <c r="D16" s="4" t="str">
         <f>_xlfn.XLOOKUP(C16,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Platinum II</v>
+        <v>Platinum III</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>5</v>
@@ -983,11 +983,11 @@
         <v>4713</v>
       </c>
       <c r="C17" s="4">
-        <v>1080</v>
+        <v>1238</v>
       </c>
       <c r="D17" s="4" t="str">
         <f>_xlfn.XLOOKUP(C17,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Iron I</v>
+        <v>Iron III</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>5</v>
@@ -1001,11 +1001,11 @@
         <v>6455</v>
       </c>
       <c r="C18" s="4">
-        <v>2393</v>
+        <v>2620</v>
       </c>
       <c r="D18" s="4" t="str">
         <f>_xlfn.XLOOKUP(C18,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Platinum II</v>
+        <v>Diamond II</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>5</v>
@@ -1019,11 +1019,11 @@
         <v>2886</v>
       </c>
       <c r="C19" s="4">
-        <v>1808</v>
+        <v>2011</v>
       </c>
       <c r="D19" s="4" t="str">
         <f>_xlfn.XLOOKUP(C19,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Silver III</v>
+        <v>Gold II</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>5</v>
@@ -1037,11 +1037,11 @@
         <v>1025</v>
       </c>
       <c r="C20" s="4">
-        <v>2074</v>
+        <v>2228</v>
       </c>
       <c r="D20" s="4" t="str">
         <f>_xlfn.XLOOKUP(C20,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Gold II</v>
+        <v>Platinum I</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>5</v>
@@ -1055,11 +1055,11 @@
         <v>3528</v>
       </c>
       <c r="C21" s="4">
-        <v>1600</v>
+        <v>2187</v>
       </c>
       <c r="D21" s="4" t="str">
         <f>_xlfn.XLOOKUP(C21,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Silver I</v>
+        <v>Gold III</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>5</v>
@@ -1073,11 +1073,11 @@
         <v>168</v>
       </c>
       <c r="C22" s="4">
-        <v>2173</v>
+        <v>2380</v>
       </c>
       <c r="D22" s="4" t="str">
         <f>_xlfn.XLOOKUP(C22,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Gold III</v>
+        <v>Platinum II</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>5</v>
@@ -1091,11 +1091,11 @@
         <v>5101</v>
       </c>
       <c r="C23" s="4">
-        <v>2302</v>
+        <v>2410</v>
       </c>
       <c r="D23" s="4" t="str">
         <f>_xlfn.XLOOKUP(C23,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Platinum II</v>
+        <v>Platinum III</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>5</v>
@@ -1127,11 +1127,11 @@
         <v>6698</v>
       </c>
       <c r="C25" s="4">
-        <v>1000</v>
+        <v>1662</v>
       </c>
       <c r="D25" s="4" t="str">
         <f>_xlfn.XLOOKUP(C25,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Iron I</v>
+        <v>Silver I</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>5</v>
@@ -1145,11 +1145,11 @@
         <v>8128</v>
       </c>
       <c r="C26" s="4">
-        <v>2513</v>
+        <v>2811</v>
       </c>
       <c r="D26" s="4" t="str">
         <f>_xlfn.XLOOKUP(C26,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Diamond I</v>
+        <v>Master I</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>5</v>
@@ -1181,11 +1181,11 @@
         <v>452</v>
       </c>
       <c r="C28" s="4">
-        <v>2111</v>
+        <v>2624</v>
       </c>
       <c r="D28" s="4" t="str">
         <f>_xlfn.XLOOKUP(C28,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Gold III</v>
+        <v>Diamond II</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>5</v>
@@ -1199,11 +1199,11 @@
         <v>9881</v>
       </c>
       <c r="C29" s="4">
-        <v>2066</v>
+        <v>2287</v>
       </c>
       <c r="D29" s="4" t="str">
         <f>_xlfn.XLOOKUP(C29,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Gold II</v>
+        <v>Platinum I</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>5</v>
@@ -1217,11 +1217,11 @@
         <v>7411</v>
       </c>
       <c r="C30" s="4">
-        <v>2365</v>
+        <v>2503</v>
       </c>
       <c r="D30" s="4" t="str">
         <f>_xlfn.XLOOKUP(C30,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Platinum II</v>
+        <v>Diamond I</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>5</v>
@@ -1252,12 +1252,12 @@
       <c r="B32" s="4">
         <v>8334</v>
       </c>
-      <c r="C32" s="4">
-        <v>1640</v>
-      </c>
-      <c r="D32" s="4" t="str">
+      <c r="C32" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D32" s="4" t="e">
         <f>_xlfn.XLOOKUP(C32,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Silver I</v>
+        <v>#N/A</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>71</v>
@@ -1306,12 +1306,12 @@
       <c r="B35" s="4">
         <v>5297</v>
       </c>
-      <c r="C35" s="4">
-        <v>1840</v>
-      </c>
-      <c r="D35" s="4" t="str">
+      <c r="C35" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D35" s="4" t="e">
         <f>_xlfn.XLOOKUP(C35,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Silver III</v>
+        <v>#N/A</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>71</v>
